--- a/etheria_restart.xlsx
+++ b/etheria_restart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvg-fight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1494" documentId="13_ncr:1_{BB734052-C730-434C-A607-24951B158975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{124FF5F0-8417-4270-B4E4-9E7E94E45698}"/>
+  <xr:revisionPtr revIDLastSave="1516" documentId="13_ncr:1_{BB734052-C730-434C-A607-24951B158975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5984A127-6F74-49C4-9EEA-FBD85966D9D2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{7D89B41E-7404-47EB-B8F5-ABCE13AB4321}"/>
   </bookViews>
@@ -44,7 +44,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="103">
+  <futureMetadata name="XLRICHVALUE" count="104">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -766,8 +766,15 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="103"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="103">
+  <valueMetadata count="104">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -1076,13 +1083,16 @@
     </bk>
     <bk>
       <rc t="1" v="102"/>
+    </bk>
+    <bk>
+      <rc t="1" v="103"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1691" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1705" uniqueCount="237">
   <si>
     <t>Animus</t>
   </si>
@@ -1492,9 +1502,6 @@
     <t xml:space="preserve">Nathenn (เร็วสุด) Skill 3 → Asal Skill 3 ใส่ Lowan →  Areal Skill 3 → หาจังหวะ Execute [ลำดับการฆ่า XC, Lowan, Areal] </t>
   </si>
   <si>
-    <t xml:space="preserve">Sylvia (เร็วสุด) Reset &amp; Buff ใส่ Lowan → Lowan Mark Nathenn → Sylvia Reset → Piayera Skill 3 &amp; 2 → Lowan Skill 2 [ลำดับการฆ่า Nathenn, Kethos, Sylvia] </t>
-  </si>
-  <si>
     <t xml:space="preserve">Sylvia (เร็วสุด) Reset &amp; Buff ใส่ Sharon → Sharon Skill 3 → Nathenn Skill 3 → Nathenn ตีธรรมดา XC → Sharon Skill 3 → หาจังหวะ Execute [ลำดับการฆ่า XC, Sharon, Areal] </t>
   </si>
   <si>
@@ -1787,13 +1794,22 @@
   </si>
   <si>
     <t xml:space="preserve">Danvery (เร็วสุด) Skill 3 ใส่ Areal → Asal Skill 3 ใส่ XL → Lingluo ตีธรรดา → Danvery Skill 2 → Dan คอยตีดึงเกจ Aseal → Asal Skill 2 → Lingluo Skill 2 → เน้นจัดการ XL เป็นหลัก [ลำดับการฆ่า XL, Luvia, Areal] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sylvia (เร็วสุด) Reset &amp; Buff ใส่ Lowan → Lowan Mark Nathenn → Piayera Skill 3 &amp; 2 → Lowan Skill 2 [ลำดับการฆ่า Nathenn, Kethos, Sylvia] </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=y3xuxFpaOoY</t>
+  </si>
+  <si>
+    <t>Jolt</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1846,6 +1862,14 @@
       <b/>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1907,10 +1931,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1972,8 +1997,12 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2142,7 +2171,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="103">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="104">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -2553,6 +2582,10 @@
   </rv>
   <rv s="0">
     <v>102</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>103</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -2672,6 +2705,7 @@
   <rel r:id="rId101"/>
   <rel r:id="rId102"/>
   <rel r:id="rId103"/>
+  <rel r:id="rId104"/>
 </richValueRels>
 </file>
 
@@ -2992,7 +3026,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33F8EE7B-7B28-4194-BF71-6AB7143EE20B}">
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.5546875" style="10" bestFit="1" customWidth="1"/>
@@ -3368,7 +3402,7 @@
     </row>
     <row r="28" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
-        <v>52</v>
+        <v>236</v>
       </c>
       <c r="B28" s="1" t="e" vm="51">
         <v>#VALUE!</v>
@@ -3376,7 +3410,7 @@
     </row>
     <row r="29" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B29" s="1" t="e" vm="52">
         <v>#VALUE!</v>
@@ -3384,7 +3418,7 @@
     </row>
     <row r="30" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B30" s="1" t="e" vm="53">
         <v>#VALUE!</v>
@@ -3392,7 +3426,7 @@
     </row>
     <row r="31" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B31" s="1" t="e" vm="54">
         <v>#VALUE!</v>
@@ -3400,7 +3434,7 @@
     </row>
     <row r="32" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B32" s="1" t="e" vm="55">
         <v>#VALUE!</v>
@@ -3408,7 +3442,7 @@
     </row>
     <row r="33" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B33" s="1" t="e" vm="56">
         <v>#VALUE!</v>
@@ -3416,7 +3450,7 @@
     </row>
     <row r="34" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B34" s="1" t="e" vm="57">
         <v>#VALUE!</v>
@@ -3424,7 +3458,7 @@
     </row>
     <row r="35" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B35" s="1" t="e" vm="58">
         <v>#VALUE!</v>
@@ -3432,7 +3466,7 @@
     </row>
     <row r="36" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B36" s="1" t="e" vm="59">
         <v>#VALUE!</v>
@@ -3440,7 +3474,7 @@
     </row>
     <row r="37" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B37" s="1" t="e" vm="60">
         <v>#VALUE!</v>
@@ -3448,7 +3482,7 @@
     </row>
     <row r="38" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B38" s="1" t="e" vm="61">
         <v>#VALUE!</v>
@@ -3456,7 +3490,7 @@
     </row>
     <row r="39" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B39" s="1" t="e" vm="62">
         <v>#VALUE!</v>
@@ -3464,7 +3498,7 @@
     </row>
     <row r="40" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B40" s="1" t="e" vm="63">
         <v>#VALUE!</v>
@@ -3472,7 +3506,7 @@
     </row>
     <row r="41" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B41" s="1" t="e" vm="64">
         <v>#VALUE!</v>
@@ -3480,7 +3514,7 @@
     </row>
     <row r="42" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B42" s="1" t="e" vm="65">
         <v>#VALUE!</v>
@@ -3488,7 +3522,7 @@
     </row>
     <row r="43" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B43" s="1" t="e" vm="66">
         <v>#VALUE!</v>
@@ -3496,7 +3530,7 @@
     </row>
     <row r="44" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B44" s="1" t="e" vm="67">
         <v>#VALUE!</v>
@@ -3504,23 +3538,23 @@
     </row>
     <row r="45" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B45" s="1" t="e" vm="68">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B45" s="1" t="e" vm="68">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="8" t="s">
+      <c r="B46" s="1" t="e" vm="69">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="8" t="s">
         <v>70</v>
-      </c>
-      <c r="B46" s="1" t="e" vm="69">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="6" t="s">
-        <v>71</v>
       </c>
       <c r="B47" s="1" t="e" vm="70">
         <v>#VALUE!</v>
@@ -3528,7 +3562,7 @@
     </row>
     <row r="48" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B48" s="1" t="e" vm="71">
         <v>#VALUE!</v>
@@ -3536,7 +3570,7 @@
     </row>
     <row r="49" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B49" s="1" t="e" vm="72">
         <v>#VALUE!</v>
@@ -3544,7 +3578,7 @@
     </row>
     <row r="50" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B50" s="1" t="e" vm="73">
         <v>#VALUE!</v>
@@ -3552,31 +3586,31 @@
     </row>
     <row r="51" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="B51" s="24" t="e" vm="74">
+        <v>74</v>
+      </c>
+      <c r="B51" s="1" t="e" vm="74">
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="B52" s="24" t="e" vm="75">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B52" s="1" t="e" vm="75">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="8" t="s">
+      <c r="B53" s="1" t="e" vm="76">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="8" t="s">
         <v>76</v>
-      </c>
-      <c r="B53" s="1" t="e" vm="76">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="B54" s="1" t="e" vm="77">
         <v>#VALUE!</v>
@@ -3584,7 +3618,7 @@
     </row>
     <row r="55" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B55" s="1" t="e" vm="78">
         <v>#VALUE!</v>
@@ -3592,7 +3626,7 @@
     </row>
     <row r="56" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B56" s="1" t="e" vm="79">
         <v>#VALUE!</v>
@@ -3600,7 +3634,7 @@
     </row>
     <row r="57" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B57" s="1" t="e" vm="80">
         <v>#VALUE!</v>
@@ -3608,7 +3642,7 @@
     </row>
     <row r="58" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B58" s="1" t="e" vm="81">
         <v>#VALUE!</v>
@@ -3616,7 +3650,7 @@
     </row>
     <row r="59" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B59" s="1" t="e" vm="82">
         <v>#VALUE!</v>
@@ -3624,7 +3658,7 @@
     </row>
     <row r="60" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B60" s="1" t="e" vm="83">
         <v>#VALUE!</v>
@@ -3632,7 +3666,7 @@
     </row>
     <row r="61" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B61" s="1" t="e" vm="84">
         <v>#VALUE!</v>
@@ -3640,7 +3674,7 @@
     </row>
     <row r="62" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B62" s="1" t="e" vm="85">
         <v>#VALUE!</v>
@@ -3648,7 +3682,7 @@
     </row>
     <row r="63" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B63" s="1" t="e" vm="86">
         <v>#VALUE!</v>
@@ -3656,7 +3690,7 @@
     </row>
     <row r="64" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B64" s="1" t="e" vm="87">
         <v>#VALUE!</v>
@@ -3664,7 +3698,7 @@
     </row>
     <row r="65" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B65" s="1" t="e" vm="88">
         <v>#VALUE!</v>
@@ -3672,7 +3706,7 @@
     </row>
     <row r="66" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B66" s="1" t="e" vm="89">
         <v>#VALUE!</v>
@@ -3680,23 +3714,23 @@
     </row>
     <row r="67" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B67" s="1" t="e" vm="90">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B67" s="1" t="e" vm="90">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="8" t="s">
+      <c r="B68" s="1" t="e" vm="91">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="8" t="s">
         <v>91</v>
-      </c>
-      <c r="B68" s="1" t="e" vm="91">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="6" t="s">
-        <v>92</v>
       </c>
       <c r="B69" s="1" t="e" vm="92">
         <v>#VALUE!</v>
@@ -3704,7 +3738,7 @@
     </row>
     <row r="70" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B70" s="1" t="e" vm="93">
         <v>#VALUE!</v>
@@ -3712,7 +3746,7 @@
     </row>
     <row r="71" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B71" s="1" t="e" vm="94">
         <v>#VALUE!</v>
@@ -3720,7 +3754,7 @@
     </row>
     <row r="72" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B72" s="1" t="e" vm="95">
         <v>#VALUE!</v>
@@ -3728,7 +3762,7 @@
     </row>
     <row r="73" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B73" s="1" t="e" vm="96">
         <v>#VALUE!</v>
@@ -3736,7 +3770,7 @@
     </row>
     <row r="74" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B74" s="1" t="e" vm="97">
         <v>#VALUE!</v>
@@ -3744,7 +3778,7 @@
     </row>
     <row r="75" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B75" s="1" t="e" vm="98">
         <v>#VALUE!</v>
@@ -3752,7 +3786,7 @@
     </row>
     <row r="76" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B76" s="1" t="e" vm="99">
         <v>#VALUE!</v>
@@ -3760,23 +3794,23 @@
     </row>
     <row r="77" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B77" s="9" t="e" vm="100">
+        <v>99</v>
+      </c>
+      <c r="B77" s="1" t="e" vm="100">
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="78" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="B78" s="1" t="e" vm="101">
+        <v>100</v>
+      </c>
+      <c r="B78" s="9" t="e" vm="101">
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="79" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B79" s="1" t="e" vm="102">
         <v>#VALUE!</v>
@@ -3784,9 +3818,17 @@
     </row>
     <row r="80" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B80" s="1" t="e" vm="103">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B80" s="1" t="e" vm="103">
+      <c r="B81" s="1" t="e" vm="104">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -3798,7 +3840,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9C8DF62-D3A8-45C5-B4BC-03270E337BE8}">
-  <dimension ref="A1:M122"/>
+  <dimension ref="A1:M123"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.77734375" style="18" bestFit="1" customWidth="1"/>
@@ -3977,7 +4019,7 @@
         <v>29</v>
       </c>
       <c r="M4" s="23" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
@@ -4797,7 +4839,7 @@
         <v>13</v>
       </c>
       <c r="M24" s="23" t="s">
-        <v>136</v>
+        <v>234</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -4838,7 +4880,7 @@
         <v>29</v>
       </c>
       <c r="M25" s="23" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -4879,7 +4921,7 @@
         <v>35</v>
       </c>
       <c r="M26" s="23" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -4920,7 +4962,7 @@
         <v>35</v>
       </c>
       <c r="M27" s="23" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -4961,7 +5003,7 @@
         <v>13</v>
       </c>
       <c r="M28" s="23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -5002,7 +5044,7 @@
         <v>27</v>
       </c>
       <c r="M29" s="23" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -5043,7 +5085,7 @@
         <v>7</v>
       </c>
       <c r="M30" s="23" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -5084,7 +5126,7 @@
         <v>29</v>
       </c>
       <c r="M31" s="23" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -5125,7 +5167,7 @@
         <v>13</v>
       </c>
       <c r="M32" s="23" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -5166,7 +5208,7 @@
         <v>29</v>
       </c>
       <c r="M33" s="23" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -5207,7 +5249,7 @@
         <v>23</v>
       </c>
       <c r="M34" s="23" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
@@ -5248,7 +5290,7 @@
         <v>35</v>
       </c>
       <c r="M35" s="23" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -5289,7 +5331,7 @@
         <v>19</v>
       </c>
       <c r="M36" s="23" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -5330,7 +5372,7 @@
         <v>29</v>
       </c>
       <c r="M37" s="23" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -5371,7 +5413,7 @@
         <v>19</v>
       </c>
       <c r="M38" s="23" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
@@ -5412,7 +5454,7 @@
         <v>7</v>
       </c>
       <c r="M39" s="23" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -5453,7 +5495,7 @@
         <v>35</v>
       </c>
       <c r="M40" s="23" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -5494,7 +5536,7 @@
         <v>35</v>
       </c>
       <c r="M41" s="23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -5535,7 +5577,7 @@
         <v>35</v>
       </c>
       <c r="M42" s="23" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -5576,7 +5618,7 @@
         <v>13</v>
       </c>
       <c r="M43" s="23" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -5617,7 +5659,7 @@
         <v>15</v>
       </c>
       <c r="M44" s="23" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
@@ -5658,7 +5700,7 @@
         <v>15</v>
       </c>
       <c r="M45" s="23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -5699,7 +5741,7 @@
         <v>19</v>
       </c>
       <c r="M46" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -5740,7 +5782,7 @@
         <v>43</v>
       </c>
       <c r="M47" s="23" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -5781,7 +5823,7 @@
         <v>3</v>
       </c>
       <c r="M48" s="23" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -5822,7 +5864,7 @@
         <v>11</v>
       </c>
       <c r="M49" s="23" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -5863,7 +5905,7 @@
         <v>7</v>
       </c>
       <c r="M50" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -5904,7 +5946,7 @@
         <v>29</v>
       </c>
       <c r="M51" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -5945,7 +5987,7 @@
         <v>27</v>
       </c>
       <c r="M52" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -5986,7 +6028,7 @@
         <v>23</v>
       </c>
       <c r="M53" s="23" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -6027,7 +6069,7 @@
         <v>27</v>
       </c>
       <c r="M54" s="23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -6068,7 +6110,7 @@
         <v>43</v>
       </c>
       <c r="M55" s="23" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.3">
@@ -6109,7 +6151,7 @@
         <v>15</v>
       </c>
       <c r="M56" s="23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -6150,7 +6192,7 @@
         <v>7</v>
       </c>
       <c r="M57" s="23" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -6191,7 +6233,7 @@
         <v>29</v>
       </c>
       <c r="M58" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.3">
@@ -6232,7 +6274,7 @@
         <v>35</v>
       </c>
       <c r="M59" s="23" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -6273,7 +6315,7 @@
         <v>7</v>
       </c>
       <c r="M60" s="23" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -6314,7 +6356,7 @@
         <v>35</v>
       </c>
       <c r="M61" s="23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -6355,7 +6397,7 @@
         <v>13</v>
       </c>
       <c r="M62" s="23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -6396,7 +6438,7 @@
         <v>11</v>
       </c>
       <c r="M63" s="23" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -6437,7 +6479,7 @@
         <v>23</v>
       </c>
       <c r="M64" s="23" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -6478,7 +6520,7 @@
         <v>7</v>
       </c>
       <c r="M65" s="23" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -6519,7 +6561,7 @@
         <v>11</v>
       </c>
       <c r="M66" s="23" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -6560,7 +6602,7 @@
         <v>35</v>
       </c>
       <c r="M67" s="23" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -6601,7 +6643,7 @@
         <v>27</v>
       </c>
       <c r="M68" s="23" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -6642,7 +6684,7 @@
         <v>29</v>
       </c>
       <c r="M69" s="23" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -6683,7 +6725,7 @@
         <v>35</v>
       </c>
       <c r="M70" s="23" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -6765,7 +6807,7 @@
         <v>13</v>
       </c>
       <c r="M72" s="23" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -6806,7 +6848,7 @@
         <v>29</v>
       </c>
       <c r="M73" s="23" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -6847,7 +6889,7 @@
         <v>37</v>
       </c>
       <c r="M74" s="23" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="75" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -6864,7 +6906,7 @@
         <v>11</v>
       </c>
       <c r="E75" s="19" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F75" s="20" t="s">
         <v>7</v>
@@ -6888,7 +6930,7 @@
         <v>7</v>
       </c>
       <c r="M75" s="23" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="76" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
@@ -6929,7 +6971,7 @@
         <v>7</v>
       </c>
       <c r="M76" s="23" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="77" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -6970,7 +7012,7 @@
         <v>35</v>
       </c>
       <c r="M77" s="23" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="78" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
@@ -7011,7 +7053,7 @@
         <v>13</v>
       </c>
       <c r="M78" s="23" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="79" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -7052,7 +7094,7 @@
         <v>27</v>
       </c>
       <c r="M79" s="23" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="80" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
@@ -7093,7 +7135,7 @@
         <v>7</v>
       </c>
       <c r="M80" s="23" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="81" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -7134,7 +7176,7 @@
         <v>23</v>
       </c>
       <c r="M81" s="23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="82" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -7175,7 +7217,7 @@
         <v>13</v>
       </c>
       <c r="M82" s="23" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -7216,7 +7258,7 @@
         <v>35</v>
       </c>
       <c r="M83" s="23" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="84" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -7257,7 +7299,7 @@
         <v>7</v>
       </c>
       <c r="M84" s="23" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -7298,7 +7340,7 @@
         <v>27</v>
       </c>
       <c r="M85" s="23" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -7339,7 +7381,7 @@
         <v>13</v>
       </c>
       <c r="M86" s="23" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="87" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -7380,7 +7422,7 @@
         <v>7</v>
       </c>
       <c r="M87" s="23" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -7421,7 +7463,7 @@
         <v>29</v>
       </c>
       <c r="M88" s="23" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="89" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -7462,7 +7504,7 @@
         <v>35</v>
       </c>
       <c r="M89" s="23" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="90" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -7503,7 +7545,7 @@
         <v>29</v>
       </c>
       <c r="M90" s="23" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.3">
@@ -7544,7 +7586,7 @@
         <v>13</v>
       </c>
       <c r="M91" s="23" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="92" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -7585,7 +7627,7 @@
         <v>7</v>
       </c>
       <c r="M92" s="23" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="93" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -7626,7 +7668,7 @@
         <v>29</v>
       </c>
       <c r="M93" s="23" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="94" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -7667,7 +7709,7 @@
         <v>37</v>
       </c>
       <c r="M94" s="23" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.3">
@@ -7749,7 +7791,7 @@
         <v>7</v>
       </c>
       <c r="M96" s="23" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="97" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -7790,7 +7832,7 @@
         <v>31</v>
       </c>
       <c r="M97" s="23" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="98" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -7831,7 +7873,7 @@
         <v>11</v>
       </c>
       <c r="M98" s="23" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="99" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -7872,7 +7914,7 @@
         <v>11</v>
       </c>
       <c r="M99" s="23" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="100" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -7913,7 +7955,7 @@
         <v>31</v>
       </c>
       <c r="M100" s="23" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="101" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -7954,7 +7996,7 @@
         <v>3</v>
       </c>
       <c r="M101" s="23" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.3">
@@ -7995,7 +8037,7 @@
         <v>35</v>
       </c>
       <c r="M102" s="23" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="103" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -8036,7 +8078,7 @@
         <v>7</v>
       </c>
       <c r="M103" s="23" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="104" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -8077,7 +8119,7 @@
         <v>13</v>
       </c>
       <c r="M104" s="23" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="105" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -8118,7 +8160,7 @@
         <v>13</v>
       </c>
       <c r="M105" s="23" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="106" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -8159,7 +8201,7 @@
         <v>29</v>
       </c>
       <c r="M106" s="23" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="107" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -8200,7 +8242,7 @@
         <v>13</v>
       </c>
       <c r="M107" s="23" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="108" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -8241,7 +8283,7 @@
         <v>37</v>
       </c>
       <c r="M108" s="23" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="109" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -8282,7 +8324,7 @@
         <v>11</v>
       </c>
       <c r="M109" s="23" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="110" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -8323,7 +8365,7 @@
         <v>13</v>
       </c>
       <c r="M110" s="23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="111" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -8364,7 +8406,7 @@
         <v>7</v>
       </c>
       <c r="M111" s="23" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="112" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -8405,7 +8447,7 @@
         <v>11</v>
       </c>
       <c r="M112" s="23" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="113" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -8446,7 +8488,7 @@
         <v>7</v>
       </c>
       <c r="M113" s="23" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="114" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -8487,7 +8529,7 @@
         <v>23</v>
       </c>
       <c r="M114" s="23" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="115" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -8528,7 +8570,7 @@
         <v>7</v>
       </c>
       <c r="M115" s="23" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="116" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -8569,7 +8611,7 @@
         <v>43</v>
       </c>
       <c r="M116" s="23" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -8610,7 +8652,7 @@
         <v>41</v>
       </c>
       <c r="M117" s="23" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="118" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -8651,7 +8693,7 @@
         <v>23</v>
       </c>
       <c r="M118" s="23" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="119" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -8692,7 +8734,7 @@
         <v>7</v>
       </c>
       <c r="M119" s="23" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="120" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -8733,7 +8775,7 @@
         <v>43</v>
       </c>
       <c r="M120" s="23" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="121" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -8774,7 +8816,7 @@
         <v>29</v>
       </c>
       <c r="M121" s="23" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="122" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -8815,25 +8857,69 @@
         <v>23</v>
       </c>
       <c r="M122" s="23" t="s">
-        <v>234</v>
+        <v>233</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A123" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B123" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C123" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="D123" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E123" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="F123" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="G123" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="H123" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I123" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="J123" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="K123" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="L123" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="M123" s="25" t="s">
+        <v>235</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="M123" r:id="rId1" xr:uid="{0CCB6433-33DF-4324-A2E6-9521CFE3AFB1}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CA26D47E-6623-4B72-A42C-17472717221A}">
           <x14:formula1>
-            <xm:f>Information!$A$1:$A$80</xm:f>
+            <xm:f>Information!$A$1:$A$81</xm:f>
           </x14:formula1>
-          <xm:sqref>A2:A122 G2:G122 K2:K122 E2:E122 I2:I122 C2:C122</xm:sqref>
+          <xm:sqref>A2:A123 C2:C123 I2:I123 E2:E123 K2:K123 G2:G123</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9E62CDE2-36BB-41FB-BCF8-DB5FFAD0C581}">
           <x14:formula1>
             <xm:f>Information!$D$1:$D$25</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F122 H2:H122 L2:L122 J2:J122 D2:D122 B2:B122</xm:sqref>
+          <xm:sqref>F2:F123 H2:H123 L2:L123 J2:J123 D2:D123 B2:B123</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/etheria_restart.xlsx
+++ b/etheria_restart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvg-fight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1516" documentId="13_ncr:1_{BB734052-C730-434C-A607-24951B158975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5984A127-6F74-49C4-9EEA-FBD85966D9D2}"/>
+  <xr:revisionPtr revIDLastSave="1519" documentId="13_ncr:1_{BB734052-C730-434C-A607-24951B158975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0737880-1728-4D18-8DAE-B1A8011CF4FE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{7D89B41E-7404-47EB-B8F5-ABCE13AB4321}"/>
   </bookViews>
@@ -1092,7 +1092,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1705" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1704" uniqueCount="236">
   <si>
     <t>Animus</t>
   </si>
@@ -1797,9 +1797,6 @@
   </si>
   <si>
     <t xml:space="preserve">Sylvia (เร็วสุด) Reset &amp; Buff ใส่ Lowan → Lowan Mark Nathenn → Piayera Skill 3 &amp; 2 → Lowan Skill 2 [ลำดับการฆ่า Nathenn, Kethos, Sylvia] </t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=y3xuxFpaOoY</t>
   </si>
   <si>
     <t>Jolt</t>
@@ -2124,10 +2121,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3402,7 +3395,7 @@
     </row>
     <row r="28" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B28" s="1" t="e" vm="51">
         <v>#VALUE!</v>
@@ -8897,14 +8890,12 @@
       <c r="L123" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="M123" s="25" t="s">
-        <v>235</v>
+      <c r="M123" s="25" t="str">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=y3xuxFpaOoY", "https://www.youtube.com/watch?v=y3xuxFpaOoY")</f>
+        <v>https://www.youtube.com/watch?v=y3xuxFpaOoY</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="M123" r:id="rId1" xr:uid="{0CCB6433-33DF-4324-A2E6-9521CFE3AFB1}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
